--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2019_los_lagos.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2019_los_lagos.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:00</t>
+    <t xml:space="preserve">2026-09-09 19:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2019_los_lagos.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2019_los_lagos.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:32</t>
+    <t xml:space="preserve">2026-09-16 16:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2019_los_lagos.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2019_los_lagos.xlsx
@@ -6,29 +6,32 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sexo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Edades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Comunas" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Edades'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comunas'!$A$1:$D$31</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <si>
-    <t xml:space="preserve">Categoría</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saldo migratorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hombres</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mujeres</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+  <si>
+    <t xml:space="preserve">Cambiaron de comuna dentro de la región</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cruzaron el límite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llegaron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se fueron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo de la región</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -40,7 +43,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-16 16:32</t>
+    <t xml:space="preserve">2026-09-30 09:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -58,31 +61,121 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">M_SALDOMIGR_a</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Región de Los Lagos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
   </si>
   <si>
-    <t xml:space="preserve">Tramo de edad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 a 4 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 a 14 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15 a 29 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 a 59 años</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60 años o más</t>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con otras regiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con otras comunas de la región</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saldo de la comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Montt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osorno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Castro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futaleufú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puqueldón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Negro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochamó</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queilén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaitén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puyehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pablo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frutillar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalcahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quemchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Juan de la Costa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chonchi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calbuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maullín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Octay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purranque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualaihué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llanquihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Varas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Muermos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quellón</t>
   </si>
 </sst>
 </file>
@@ -447,8 +540,11 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="11.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="40.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="11.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,25 +554,35 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
+      <c r="A2" s="2" t="n">
+        <v>21806</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>641</v>
+        <v>38071</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>19655</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>18416</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1239</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:E2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -493,58 +599,58 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -558,60 +664,448 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="18.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="32.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>36</v>
+        <v>524</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1377</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1901</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>348</v>
+        <v>499</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>470</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>969</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>294</v>
+        <v>24</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>291</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>315</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>630</v>
+        <v>75</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>-17</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>21</v>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>-69</v>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>-18</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>-19</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>-89</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>-65</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-39</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>-72</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>-31</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>-25</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-56</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>-73</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>-11</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>-51</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>-79</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>-68</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>-96</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>-72</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>-126</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>-93</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>-197</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>-98</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>-18</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>-96</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>-114</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>-135</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>-118</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>-97</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>-24</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>-121</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>-147</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>-142</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>-174</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>-155</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>-30</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>-156</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>-186</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>-258</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>-237</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>-51</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>-188</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>-239</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>-46</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>-213</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>-259</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:D31"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>

--- a/output/graficos_regionales_migracion/plot_migracion_saldo_se_2019_los_lagos.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_saldo_se_2019_los_lagos.xlsx
@@ -43,7 +43,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 09:55</t>
+    <t xml:space="preserve">2026-10-05 03:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
